--- a/excel_templates/approval.xlsx
+++ b/excel_templates/approval.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="14625" windowHeight="6900"/>
+    <workbookView windowWidth="18330" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="公章审批" sheetId="21" r:id="rId1"/>
@@ -310,18 +310,12 @@
       <charset val="2"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -650,7 +644,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -674,16 +668,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -692,88 +686,88 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -818,11 +812,11 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -836,36 +830,55 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="55" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="55" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="55" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="55" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="55" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="55" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="55" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="55" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="55" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="55" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="55" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="55" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="55" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="55" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="55" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="55" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="55" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="55" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="65">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1230,7 +1243,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" ht="20.25" spans="1:9">
@@ -1260,161 +1273,179 @@
     <row r="3" ht="18.75" spans="1:9">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
     </row>
     <row r="4" ht="18.75" spans="1:9">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="7" t="s">
+      <c r="B4" s="8"/>
+      <c r="C4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="5" t="s">
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="11">
         <f ca="1">TODAY()</f>
         <v>46097</v>
       </c>
-      <c r="I4" s="8"/>
+      <c r="I4" s="11"/>
     </row>
     <row r="5" ht="18.75" spans="1:9">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
     </row>
     <row r="6" ht="18.75" spans="1:9">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
     </row>
     <row r="7" ht="18.75" spans="1:9">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
     </row>
     <row r="8" ht="18.75" spans="1:9">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="5" t="s">
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
     </row>
     <row r="9" ht="18.75" spans="1:9">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
     </row>
     <row r="10" ht="18.75" spans="1:9">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="11" t="s">
+      <c r="B10" s="15"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
     </row>
     <row r="11" ht="18.75" spans="1:9">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="3"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="6"/>
     </row>
     <row r="12" ht="18.75" spans="1:9">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
     </row>
     <row r="13" ht="18.75" spans="1:9">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="3"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="6"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/excel_templates/approval.xlsx
+++ b/excel_templates/approval.xlsx
@@ -44,13 +44,13 @@
     <t>相关内容或单证号：</t>
   </si>
   <si>
-    <t>{{Contract No.}}</t>
+    <t>{{Contract_No.}}</t>
   </si>
   <si>
     <t>客户名称：</t>
   </si>
   <si>
-    <t>{{Proxy client}}</t>
+    <t>{{Proxy_client}}</t>
   </si>
   <si>
     <t>业务员：</t>
@@ -816,7 +816,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -856,9 +856,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="55" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="55" applyFont="1">
       <alignment vertical="center"/>
@@ -1297,7 +1294,7 @@
       </c>
       <c r="H4" s="11">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="I4" s="11"/>
     </row>
@@ -1352,8 +1349,8 @@
       <c r="G8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
     </row>
     <row r="9" ht="18.75" spans="1:9">
       <c r="A9" s="4"/>
@@ -1367,31 +1364,31 @@
       <c r="I9" s="6"/>
     </row>
     <row r="10" ht="18.75" spans="1:9">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="15"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
     </row>
     <row r="11" ht="18.75" spans="1:9">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="18"/>
       <c r="I11" s="6"/>
     </row>
     <row r="12" ht="18.75" spans="1:9">
@@ -1409,23 +1406,23 @@
       <c r="A13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
       <c r="E13" s="10"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="19"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="18"/>
       <c r="I13" s="6"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="3"/>
@@ -1439,13 +1436,13 @@
       <c r="I15" s="6"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/excel_templates/approval.xlsx
+++ b/excel_templates/approval.xlsx
@@ -44,7 +44,7 @@
     <t>相关内容或单证号：</t>
   </si>
   <si>
-    <t>{{Contract_No.}}</t>
+    <t>{{Contract_No}}</t>
   </si>
   <si>
     <t>客户名称：</t>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H4" s="11">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="I4" s="11"/>
     </row>
